--- a/sheets/대금율보/검수/사설 질음 시조.xlsx
+++ b/sheets/대금율보/검수/사설 질음 시조.xlsx
@@ -4296,7 +4296,7 @@
       <c r="I5" s="22"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲‹
+          <t xml:space="preserve">仲
 仲フ
 –И</t>
         </is>
@@ -4330,8 +4330,7 @@
         <is>
           <t xml:space="preserve">林∧仲
 –林ʒ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="S5" s="22"/>
@@ -4429,8 +4428,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -4438,8 +4436,7 @@
         <is>
           <t xml:space="preserve">–
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="G7" s="22"/>
@@ -4449,8 +4446,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -4458,18 +4454,13 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="21"/>
       <c r="O7" s="22"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
@@ -4648,8 +4639,7 @@
         <is>
           <t xml:space="preserve">仲⌇
 –И
-太∧
-‹</t>
+太∧</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -4659,15 +4649,13 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">И
-‹</t>
+          <t xml:space="preserve">И</t>
         </is>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃∧⌇
-‹</t>
+          <t xml:space="preserve">黃∧⌇</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -4677,8 +4665,7 @@
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲⌇
-‹</t>
+          <t xml:space="preserve">仲⌇</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -4690,8 +4677,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="M10" s="22"/>
@@ -4699,8 +4685,7 @@
         <is>
           <t xml:space="preserve">汰潢И
 南⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O10" s="22" t="inlineStr">
@@ -4712,8 +4697,7 @@
         <is>
           <t xml:space="preserve">–
 –汰
-汰フ
-‹</t>
+汰フ</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
@@ -4839,8 +4823,7 @@
         <is>
           <t xml:space="preserve">潢⌇
 –
-汰)
-‹</t>
+汰)</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -4852,8 +4835,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
@@ -4938,7 +4920,7 @@
       </c>
       <c r="L13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">?仲
+          <t xml:space="preserve">仲
 –ㄴ
 仲</t>
         </is>
@@ -5050,8 +5032,7 @@
         <is>
           <t xml:space="preserve">黃∧И
 㑲
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -5063,8 +5044,7 @@
         <is>
           <t xml:space="preserve">黃ʒ̵⌇
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="G15" s="24"/>
@@ -5096,8 +5076,7 @@
         <is>
           <t xml:space="preserve">黃フ⌇
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="M15" s="22"/>
@@ -5105,8 +5084,7 @@
         <is>
           <t xml:space="preserve">仲林∧
 南林
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">

--- a/sheets/대금율보/검수/사설 질음 시조.xlsx
+++ b/sheets/대금율보/검수/사설 질음 시조.xlsx
@@ -4046,30 +4046,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="141.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="141.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="141.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="141.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="141.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="141.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="141.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4631,7 +4631,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="141.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4704,7 +4704,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="141.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4783,7 +4783,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="141.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4866,7 +4866,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="141.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4951,7 +4951,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="141.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -5024,7 +5024,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="141.22" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5109,6 +5109,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>